--- a/outputs/daily/hr_rankings_2026-08-05_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-05_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -23431,52 +23431,52 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-05T18:10:00Z</t>
+          <t>2026-08-06T01:40:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -23494,61 +23494,65 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>51.5</v>
+        <v>45.7</v>
       </c>
       <c r="Q84" t="n">
-        <v>24.1</v>
+        <v>38.2</v>
       </c>
       <c r="R84" t="n">
-        <v>41.6</v>
+        <v>28.2</v>
       </c>
       <c r="S84" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T84" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U84" t="n">
-        <v>44.8</v>
+        <v>32</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr"/>
@@ -23570,137 +23574,129 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>48.61</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>101.8356</t>
+          <t>101.4652</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.3315</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.1947</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>23.16</t>
-        </is>
-      </c>
-      <c r="BG84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH84" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -23711,47 +23707,47 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-06T01:40:00Z</t>
+          <t>2026-08-05T18:35:00Z</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>687931</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -23760,7 +23756,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -23774,65 +23770,61 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>45.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>38.2</v>
+        <v>69.8</v>
       </c>
       <c r="R85" t="n">
-        <v>28.2</v>
+        <v>42.1</v>
       </c>
       <c r="S85" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T85" t="n">
         <v>78</v>
       </c>
       <c r="U85" t="n">
-        <v>32</v>
+        <v>21.8</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr"/>
@@ -23849,27 +23841,27 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 2/14, 1 HR</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 4.6 HR allowed</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -23879,104 +23871,112 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>48.61</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>86.65</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>101.4652</t>
+          <t>99.3042</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3522</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>0.3315</t>
+          <t>0.2687</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>0.1947</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>90.51</t>
         </is>
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.5387</t>
         </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.2494</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="BG85" t="inlineStr"/>
-      <c r="BH85" t="inlineStr"/>
+          <t>33.26</t>
+        </is>
+      </c>
+      <c r="BG85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI85" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ85" t="inlineStr"/>
@@ -23987,52 +23987,52 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-05T18:35:00Z</t>
+          <t>2026-08-05T23:40:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>687931</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -24050,58 +24050,62 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>23.8</v>
+        <v>46.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>69.8</v>
+        <v>46.8</v>
       </c>
       <c r="R86" t="n">
-        <v>42.1</v>
+        <v>23.2</v>
       </c>
       <c r="S86" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U86" t="n">
-        <v>21.8</v>
+        <v>48.5</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24121,12 +24125,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -24136,12 +24140,12 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/14, 1 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 4.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24151,112 +24155,104 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>43.97</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>86.65</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>99.3042</t>
+          <t>100.732</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.3522</t>
+          <t>0.4493</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.2687</t>
+          <t>0.3164</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1771</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>90.51</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.5387</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.2494</t>
+          <t>0.2114</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>33.26</t>
-        </is>
-      </c>
-      <c r="BG86" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH86" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>35.47</t>
+        </is>
+      </c>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -24267,47 +24263,47 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-05T23:40:00Z</t>
+          <t>2026-08-05T19:10:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24316,7 +24312,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24330,62 +24326,58 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>46.7</v>
+        <v>14.9</v>
       </c>
       <c r="Q87" t="n">
-        <v>46.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="R87" t="n">
-        <v>23.2</v>
+        <v>61.7</v>
       </c>
       <c r="S87" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T87" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U87" t="n">
-        <v>48.5</v>
+        <v>26.8</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24405,12 +24397,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -24420,119 +24412,127 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.3% barrel, 24.6 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>43.97</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>100.732</t>
+          <t>96.7987</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.4493</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.1025</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.3164</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1771</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.5576</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.2114</t>
+          <t>0.2497</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>35.47</t>
-        </is>
-      </c>
-      <c r="BG87" t="inlineStr"/>
-      <c r="BH87" t="inlineStr"/>
+          <t>29.86</t>
+        </is>
+      </c>
+      <c r="BG87" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24543,47 +24543,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-05T19:10:00Z</t>
+          <t>2026-08-05T22:40:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24592,7 +24592,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -24606,61 +24606,65 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>14.9</v>
+        <v>43.9</v>
       </c>
       <c r="Q88" t="n">
-        <v>74.59999999999999</v>
+        <v>46.5</v>
       </c>
       <c r="R88" t="n">
-        <v>61.7</v>
+        <v>34.3</v>
       </c>
       <c r="S88" t="n">
-        <v>64.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T88" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U88" t="n">
-        <v>26.8</v>
+        <v>25.3</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24677,12 +24681,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -24692,12 +24696,12 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.3% barrel, 24.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24707,112 +24711,104 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>96.7987</t>
+          <t>101.4034</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.4217</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1025</t>
+          <t>0.1839</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.3217</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1524</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.5576</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.2497</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>29.86</t>
-        </is>
-      </c>
-      <c r="BG88" t="inlineStr">
-        <is>
-          <t>Varies</t>
-        </is>
-      </c>
-      <c r="BH88" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -24823,27 +24819,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-05T22:40:00Z</t>
+          <t>2026-08-05T23:40:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -24858,17 +24854,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -24886,26 +24882,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>43.9</v>
+        <v>41.5</v>
       </c>
       <c r="Q89" t="n">
-        <v>46.5</v>
+        <v>42.9</v>
       </c>
       <c r="R89" t="n">
-        <v>34.3</v>
+        <v>23.2</v>
       </c>
       <c r="S89" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T89" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U89" t="n">
-        <v>25.3</v>
+        <v>43.2</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -24944,7 +24940,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr"/>
@@ -24961,12 +24957,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -24976,12 +24972,12 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -24991,104 +24987,104 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>101.4034</t>
+          <t>100.8804</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4217</t>
+          <t>0.4448</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.1839</t>
+          <t>0.1892</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.3217</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>73.69</t>
+          <t>72.79</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1524</t>
+          <t>0.1989</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>0.431</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25099,32 +25095,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>642715</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-05T23:40:00Z</t>
+          <t>2026-08-05T18:35:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -25134,12 +25130,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25148,7 +25144,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25162,65 +25158,61 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>41.5</v>
+        <v>37.5</v>
       </c>
       <c r="Q90" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="R90" t="n">
-        <v>23.2</v>
+        <v>42.1</v>
       </c>
       <c r="S90" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T90" t="n">
         <v>78</v>
       </c>
       <c r="U90" t="n">
-        <v>43.2</v>
+        <v>5.1</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -25237,27 +25229,27 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -25267,104 +25259,88 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>100.8804</t>
+          <t>99.0729</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.4448</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3011</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>72.21</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>23.83</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>47.91</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1989</t>
-        </is>
-      </c>
-      <c r="BA90" t="inlineStr">
-        <is>
-          <t>8.26</t>
-        </is>
-      </c>
-      <c r="BB90" t="inlineStr">
-        <is>
-          <t>38.31</t>
-        </is>
-      </c>
-      <c r="BC90" t="inlineStr">
-        <is>
-          <t>88.81</t>
-        </is>
-      </c>
-      <c r="BD90" t="inlineStr">
-        <is>
-          <t>0.431</t>
-        </is>
-      </c>
-      <c r="BE90" t="inlineStr">
-        <is>
-          <t>0.173</t>
-        </is>
-      </c>
-      <c r="BF90" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>0.1911</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr"/>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25375,32 +25351,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>642715</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-05T18:35:00Z</t>
+          <t>2026-08-06T01:40:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -25410,21 +25386,21 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25438,61 +25414,65 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>37.5</v>
+        <v>47.4</v>
       </c>
       <c r="Q91" t="n">
-        <v>41.2</v>
+        <v>40.5</v>
       </c>
       <c r="R91" t="n">
-        <v>42.1</v>
+        <v>25.4</v>
       </c>
       <c r="S91" t="n">
-        <v>96.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T91" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>5.1</v>
+        <v>55.2</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -25509,27 +25489,27 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
@@ -25539,88 +25519,104 @@
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>99.0729</t>
+          <t>100.9658</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.5009</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3011</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>72.21</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>47.91</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1911</t>
-        </is>
-      </c>
-      <c r="BA91" t="inlineStr"/>
-      <c r="BB91" t="inlineStr"/>
-      <c r="BC91" t="inlineStr"/>
-      <c r="BD91" t="inlineStr"/>
-      <c r="BE91" t="inlineStr"/>
-      <c r="BF91" t="inlineStr"/>
-      <c r="BG91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH91" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>0.2177</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>7.42</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>42.29</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>89.38</t>
+        </is>
+      </c>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>0.3807</t>
+        </is>
+      </c>
+      <c r="BE91" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF91" t="inlineStr">
+        <is>
+          <t>28.06</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -25631,27 +25627,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-06T01:40:00Z</t>
+          <t>2026-08-05T22:35:00Z</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -25661,26 +25657,26 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -25694,26 +25690,26 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="Q92" t="n">
-        <v>40.5</v>
+        <v>35.8</v>
       </c>
       <c r="R92" t="n">
-        <v>25.4</v>
+        <v>32.1</v>
       </c>
       <c r="S92" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T92" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U92" t="n">
-        <v>55.2</v>
+        <v>7.9</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -25727,7 +25723,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -25769,134 +25765,134 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/29, 0 HR</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 8.8 HR allowed</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>100.9658</t>
+          <t>100.1853</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>0.5009</t>
+          <t>0.4264</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.2097</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>71.19</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>0.2177</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD92" t="inlineStr">
         <is>
-          <t>0.3807</t>
+          <t>0.3872</t>
         </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1433</t>
         </is>
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG92" t="inlineStr"/>
       <c r="BH92" t="inlineStr"/>
       <c r="BI92" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ92" t="inlineStr"/>
@@ -25907,27 +25903,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-05T22:35:00Z</t>
+          <t>2026-08-05T23:05:00Z</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -25942,21 +25938,21 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -25974,22 +25970,22 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>48.2</v>
+        <v>47.2</v>
       </c>
       <c r="Q93" t="n">
-        <v>35.8</v>
+        <v>27.7</v>
       </c>
       <c r="R93" t="n">
-        <v>32.1</v>
+        <v>38.2</v>
       </c>
       <c r="S93" t="n">
         <v>88.7</v>
       </c>
       <c r="T93" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U93" t="n">
-        <v>7.9</v>
+        <v>29.2</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -26050,129 +26046,129 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 8.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>100.1853</t>
+          <t>100.8338</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>0.4264</t>
+          <t>0.4525</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>0.2097</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3504</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>71.19</t>
+          <t>70.72</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.54</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>30.42</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1884</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD93" t="inlineStr">
         <is>
-          <t>0.3872</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="BG93" t="inlineStr"/>
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ93" t="inlineStr"/>
@@ -26183,27 +26179,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>663886</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-05T23:05:00Z</t>
+          <t>2026-08-05T22:40:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -26213,26 +26209,26 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -26246,26 +26242,26 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>47.2</v>
+        <v>51.3</v>
       </c>
       <c r="Q94" t="n">
-        <v>27.7</v>
+        <v>20.9</v>
       </c>
       <c r="R94" t="n">
-        <v>38.2</v>
+        <v>39.3</v>
       </c>
       <c r="S94" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T94" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U94" t="n">
-        <v>29.2</v>
+        <v>50.3</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26279,7 +26275,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -26321,12 +26317,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26336,119 +26332,119 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 13.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.1% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>90.92</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>100.8338</t>
+          <t>100.5747</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.4525</t>
+          <t>0.4487</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.2068</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3504</t>
+          <t>0.3382</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>70.72</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1884</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>31.59</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>85.85</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr"/>
       <c r="BH94" t="inlineStr"/>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26459,56 +26455,56 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>663886</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-05T22:40:00Z</t>
+          <t>2026-08-05T18:10:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26522,65 +26518,61 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>20.9</v>
+        <v>24.1</v>
       </c>
       <c r="R95" t="n">
-        <v>39.3</v>
+        <v>41.6</v>
       </c>
       <c r="S95" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T95" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U95" t="n">
-        <v>50.3</v>
+        <v>22.4</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr"/>
@@ -26602,129 +26594,137 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.1% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>90.92</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>100.5747</t>
+          <t>101.8356</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.4487</t>
+          <t>0.421</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.2068</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3382</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>85.85</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>32.06</t>
-        </is>
-      </c>
-      <c r="BG95" t="inlineStr"/>
-      <c r="BH95" t="inlineStr"/>
+          <t>23.16</t>
+        </is>
+      </c>
+      <c r="BG95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH95" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -26760,7 +26760,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -26869,12 +26869,12 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -28704,7 +28704,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -28984,7 +28984,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -33412,7 +33412,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -43656,7 +43656,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -59952,7 +59952,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -61868,7 +61868,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -61977,12 +61977,12 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
@@ -61992,7 +61992,7 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 0/17, 0 HR</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
@@ -62700,7 +62700,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -70924,7 +70924,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -72032,7 +72032,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -72516,7 +72516,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -73122,7 +73122,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
